--- a/data/trans_camb/P68-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P68-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,85</t>
+          <t>-5,53; 6,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 5,38</t>
+          <t>-7,16; 5,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 0,24</t>
+          <t>-10,24; 0,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 9,72</t>
+          <t>-7,0; 9,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 8,49</t>
+          <t>-7,37; 8,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 4,07</t>
+          <t>-10,22; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,56</t>
+          <t>-4,4; 5,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 4,47</t>
+          <t>-5,38; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,71</t>
+          <t>-7,68; 0,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 37,48</t>
+          <t>-26,84; 42,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 35,32</t>
+          <t>-34,49; 33,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 1,59</t>
+          <t>-47,89; 4,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 59,06</t>
+          <t>-27,89; 57,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 48,35</t>
+          <t>-29,45; 50,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 24,71</t>
+          <t>-38,74; 22,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 31,94</t>
+          <t>-20,91; 31,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 27,07</t>
+          <t>-23,77; 27,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 4,3</t>
+          <t>-35,14; 6,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 4,91</t>
+          <t>-7,26; 5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 2,8</t>
+          <t>-9,56; 3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 7,28</t>
+          <t>-5,44; 7,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 6,82</t>
+          <t>-9,45; 6,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 5,16</t>
+          <t>-9,12; 5,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,27</t>
+          <t>-6,91; 5,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,48</t>
+          <t>-6,27; 3,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,12</t>
+          <t>-7,45; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 4,53</t>
+          <t>-4,36; 5,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 37,47</t>
+          <t>-39,15; 42,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 21,79</t>
+          <t>-50,32; 29,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 57,93</t>
+          <t>-29,41; 60,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 45,62</t>
+          <t>-45,44; 44,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 39,7</t>
+          <t>-44,11; 35,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 46,36</t>
+          <t>-32,51; 44,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 25,77</t>
+          <t>-34,4; 24,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 14,63</t>
+          <t>-39,79; 15,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 31,45</t>
+          <t>-22,62; 37,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 9,56</t>
+          <t>-4,5; 8,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 12,78</t>
+          <t>-4,16; 12,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,07; -0,75</t>
+          <t>-26,24; 0,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 15,41</t>
+          <t>-15,01; 15,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -0,57</t>
+          <t>-30,49; 0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 10,71</t>
+          <t>-18,95; 10,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 8,6</t>
+          <t>-3,71; 9,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 7,01</t>
+          <t>-6,3; 7,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,28; -1,3</t>
+          <t>-25,67; -0,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 41,04</t>
+          <t>-15,95; 37,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 54,75</t>
+          <t>-14,45; 54,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,56; -2,97</t>
+          <t>-89,95; 2,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 77,93</t>
+          <t>-37,41; 80,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 7,64</t>
+          <t>-78,25; 7,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 57,53</t>
+          <t>-49,6; 64,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 36,9</t>
+          <t>-12,72; 37,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 28,97</t>
+          <t>-21,73; 32,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,65; -2,08</t>
+          <t>-81,83; -1,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,05</t>
+          <t>-6,44; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 5,88</t>
+          <t>-5,72; 5,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 0,47</t>
+          <t>-10,02; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 13,18</t>
+          <t>0,08; 12,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 12,65</t>
+          <t>0,67; 12,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 14,1</t>
+          <t>3,22; 14,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,93</t>
+          <t>-3,66; 5,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,2</t>
+          <t>-2,8; 5,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,66</t>
+          <t>-4,52; 3,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 19,27</t>
+          <t>-20,75; 17,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 22,14</t>
+          <t>-18,93; 19,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 1,89</t>
+          <t>-32,17; 3,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 95,55</t>
+          <t>-0,53; 94,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 95,48</t>
+          <t>3,71; 96,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,34; 107,66</t>
+          <t>15,78; 109,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 21,52</t>
+          <t>-13,61; 21,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 22,84</t>
+          <t>-10,63; 22,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 15,67</t>
+          <t>-16,41; 14,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 1,8</t>
+          <t>-20,04; 2,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 10,81</t>
+          <t>-9,18; 11,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -3,36</t>
+          <t>-22,07; -1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 2,81</t>
+          <t>-15,55; 2,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 1,63</t>
+          <t>-16,69; 0,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 21,49</t>
+          <t>-13,45; 20,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -0,58</t>
+          <t>-13,9; -0,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 3,42</t>
+          <t>-9,64; 3,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 9,02</t>
+          <t>-13,38; 9,27</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 6,72</t>
+          <t>-49,42; 8,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 39,51</t>
+          <t>-23,14; 41,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -11,98</t>
+          <t>-54,99; -6,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 9,77</t>
+          <t>-43,77; 12,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 6,87</t>
+          <t>-46,15; 3,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 73,05</t>
+          <t>-38,3; 72,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,24; -2,31</t>
+          <t>-38,95; -2,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 12,22</t>
+          <t>-27,15; 10,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 31,24</t>
+          <t>-38,24; 30,3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,72; 1,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,27; 2,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,08; -3,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,52; 5,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,86; 3,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,45; 9,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,17; 1,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,88; 1,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,87; 0,17</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,69%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-29,11%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,47%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-12,92%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,83; 4,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,55; 11,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,68; -14,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,73; 25,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,69; 15,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,43; 47,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,58; 7,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,55; 7,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-32,7; 0,53</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-7,28</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 1,54</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-3,35; 2,95</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-15,1; -3,52</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 4,88</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-4,19; 3,21</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 8,88</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 1,97</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 1,97</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-7,97; 0,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>-6,51%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-0,69%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-29,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-2,66%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-2,8%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-2,47%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-12,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-17,38; 6,69</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-12,4; 12,17</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-58,76; -14,64</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-12,53; 24,42</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-17,82; 16,58</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-6,7; 43,43</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; 8,87</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 8,66</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-33,18; 0,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P68-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P68-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,87</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,54</t>
+          <t>-6,94; 6,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 5,37</t>
+          <t>-7,83; 4,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 0,51</t>
+          <t>-9,78; 1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 9,82</t>
+          <t>-6,88; 9,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 8,89</t>
+          <t>-7,9; 8,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 3,9</t>
+          <t>-9,18; 3,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,4</t>
+          <t>-4,34; 5,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,67</t>
+          <t>-5,4; 4,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,88</t>
+          <t>-7,49; 1,39</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,77%</t>
+          <t>-23,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,21%</t>
+          <t>-14,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,84%</t>
+          <t>-17,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 42,67</t>
+          <t>-32,67; 40,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 33,4</t>
+          <t>-36,8; 33,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 4,72</t>
+          <t>-46,56; 13,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 57,38</t>
+          <t>-27,92; 54,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 50,59</t>
+          <t>-30,39; 47,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 22,54</t>
+          <t>-36,81; 20,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 31,89</t>
+          <t>-20,61; 30,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 27,03</t>
+          <t>-24,82; 25,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 6,45</t>
+          <t>-34,96; 8,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,79</t>
+          <t>-7,75; 5,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 3,56</t>
+          <t>-9,52; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 7,62</t>
+          <t>-5,9; 7,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 6,3</t>
+          <t>-8,73; 6,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 5,01</t>
+          <t>-9,33; 5,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 5,92</t>
+          <t>-7,1; 5,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,59</t>
+          <t>-6,87; 3,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,06</t>
+          <t>-7,48; 1,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,21</t>
+          <t>-4,65; 4,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,76%</t>
+          <t>-5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>-0,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 42,65</t>
+          <t>-41,82; 42,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 29,93</t>
+          <t>-50,66; 26,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 60,29</t>
+          <t>-31,12; 62,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 44,32</t>
+          <t>-43,56; 44,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 35,36</t>
+          <t>-44,25; 34,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 44,86</t>
+          <t>-32,92; 38,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 24,3</t>
+          <t>-35,34; 23,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 15,13</t>
+          <t>-39,79; 14,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 37,13</t>
+          <t>-24,53; 30,89</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-14,46</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-13,09</t>
+          <t>-3,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 8,9</t>
+          <t>-5,28; 9,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 12,91</t>
+          <t>-3,11; 12,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 0,39</t>
+          <t>-10,76; 3,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 15,48</t>
+          <t>-13,79; 16,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 0,15</t>
+          <t>-28,64; 1,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 10,87</t>
+          <t>-16,92; 11,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,14</t>
+          <t>-3,97; 9,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 7,6</t>
+          <t>-6,88; 7,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -0,48</t>
+          <t>-9,52; 3,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-54,61%</t>
+          <t>-13,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,08%</t>
+          <t>-11,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,92%</t>
+          <t>-12,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 37,68</t>
+          <t>-17,47; 38,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 54,96</t>
+          <t>-10,77; 53,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,95; 2,15</t>
+          <t>-37,41; 14,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 80,54</t>
+          <t>-36,27; 89,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 7,97</t>
+          <t>-77,2; 10,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 64,85</t>
+          <t>-46,73; 61,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 37,93</t>
+          <t>-13,12; 39,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 32,14</t>
+          <t>-23,06; 32,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,83; -1,43</t>
+          <t>-33,2; 15,92</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 4,79</t>
+          <t>-6,73; 4,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,07</t>
+          <t>-5,97; 5,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,8</t>
+          <t>-8,78; 1,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 12,85</t>
+          <t>0,06; 12,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 12,53</t>
+          <t>0,69; 12,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 14,46</t>
+          <t>2,44; 12,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,05</t>
+          <t>-3,53; 5,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,32</t>
+          <t>-3,07; 5,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,44</t>
+          <t>-3,92; 3,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-15,69%</t>
+          <t>-12,39%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,42%</t>
+          <t>-1,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 17,9</t>
+          <t>-21,71; 19,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 19,15</t>
+          <t>-19,45; 21,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 3,8</t>
+          <t>-28,35; 6,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 94,11</t>
+          <t>-0,86; 91,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 96,88</t>
+          <t>2,94; 93,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,78; 109,67</t>
+          <t>11,72; 100,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 21,69</t>
+          <t>-13,35; 21,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 22,99</t>
+          <t>-11,34; 22,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 14,7</t>
+          <t>-14,33; 14,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-13,06</t>
+          <t>-13,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-5,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 2,27</t>
+          <t>-19,7; 1,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 11,4</t>
+          <t>-9,43; 10,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,07; -1,95</t>
+          <t>-22,73; -4,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 2,85</t>
+          <t>-15,9; 2,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 0,85</t>
+          <t>-15,94; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 20,62</t>
+          <t>-6,64; 9,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -0,56</t>
+          <t>-14,18; 0,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,07</t>
+          <t>-10,64; 3,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 9,27</t>
+          <t>-11,72; 0,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-37,33%</t>
+          <t>-38,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,39%</t>
+          <t>-17,17%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 8,08</t>
+          <t>-49,65; 6,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 41,25</t>
+          <t>-22,4; 36,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,99; -6,44</t>
+          <t>-54,6; -12,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 12,52</t>
+          <t>-44,09; 10,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 3,29</t>
+          <t>-45,22; 6,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 72,32</t>
+          <t>-18,51; 38,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,95; -2,09</t>
+          <t>-38,76; 1,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 10,23</t>
+          <t>-28,87; 13,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 30,3</t>
+          <t>-32,34; 0,37</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-7,28</t>
+          <t>-4,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-2,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 1,12</t>
+          <t>-4,8; 1,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,83</t>
+          <t>-3,21; 3,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -3,66</t>
+          <t>-7,51; -1,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,0</t>
+          <t>-2,41; 5,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,04</t>
+          <t>-3,75; 3,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,57</t>
+          <t>-1,64; 5,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,7</t>
+          <t>-3,09; 1,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,82</t>
+          <t>-2,73; 1,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,17</t>
+          <t>-4,0; 0,24</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,11%</t>
+          <t>-17,93%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-12,92%</t>
+          <t>-8,4%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 4,6</t>
+          <t>-18,61; 5,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 11,79</t>
+          <t>-12,53; 12,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,68; -14,97</t>
+          <t>-28,56; -6,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 25,53</t>
+          <t>-10,42; 26,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 15,43</t>
+          <t>-16,38; 17,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 47,07</t>
+          <t>-6,91; 25,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,64</t>
+          <t>-12,34; 7,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 7,8</t>
+          <t>-11,33; 8,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 0,53</t>
+          <t>-16,24; 0,95</t>
         </is>
       </c>
     </row>
